--- a/Common/doc/codegen/media/tables.xlsx
+++ b/Common/doc/codegen/media/tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Profiles\Common\doc\codgen\media\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Profiles\Common\doc\codegen\media\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2AE2AF-5AA4-4352-886A-1FCBC06E88DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668028E9-34D4-48DB-9082-4407BB3C8103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Globals" sheetId="1" r:id="rId1"/>
@@ -25,48 +25,177 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
-  <si>
-    <t>Function</t>
-  </si>
-  <si>
-    <t>Function</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
   <si>
     <t>Description</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>LOGI(string)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LOGE(string)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LOGW(string)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Prototype</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>exec(string)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>run(string)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sleep</t>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@&lt;code&gt;bool@&lt;/code&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@&lt;code&gt;string@&lt;/code&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@&lt;code&gt;IsWindows()@&lt;/code&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@&lt;code&gt;GetCommonToolPath()@&lt;/code&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@&lt;code&gt;LOGI(string msg)@&lt;/code&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@&lt;code&gt;LOGE(string msg)@&lt;/code&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@&lt;code&gt;LOGW(string msg)@&lt;/code&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@&lt;code&gt;exec(string cmd)@&lt;/code&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@&lt;code&gt;run(string cmd)@&lt;/code&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@&lt;code&gt;Sleep(int ms)@&lt;/code&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@&lt;code&gt;Pause()@&lt;/code&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@&lt;code&gt;SendMessage()@&lt;/code&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@&lt;code&gt;int@&lt;/code&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Log out as information.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Log out as error.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Log out as warnning.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>execution with return value.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sleep @&lt;code&gt;ms@&lt;/code&gt; milli-seconds.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pause in console.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Send message to window. (windows only.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Get full path string to common tool path.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Check it runs under windows OS.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function/Property Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@&lt;code&gt;log.error_count@&lt;/code&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@&lt;code&gt;log.warning_count@&lt;/code&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@&lt;code&gt;log.pause_on_error@&lt;/code&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Get count of using @&lt;code&gt;LOGE()@&lt;/code&gt; function.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Get count of using @&lt;code&gt;LOGW()@&lt;/code&gt; function.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pause when using @&lt;code&gt;LOGE()@&lt;/code&gt; function.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Get argument size of total command line input.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@&lt;code&gt;codegen.ArgumentSize()@&lt;/code&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@&lt;code&gt;codegen.GetArgument(int Index)@&lt;/code&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Get argument element of @&lt;code&gt;Index@&lt;/code&gt; order.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@&lt;code&gt;codegen.current_file@&lt;/code&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Get current Lua file name.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@&lt;code&gt;codegen.work_path@&lt;/code&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Get current working full path.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@&lt;code&gt;codegen.env_path@&lt;/code&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Get current tool path.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>execution &amp; get all log output.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -110,8 +239,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -392,61 +528,221 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="21.875" customWidth="1"/>
-    <col min="3" max="3" width="80.75" customWidth="1"/>
+    <col min="1" max="1" width="14.69921875" customWidth="1"/>
+    <col min="2" max="2" width="37.5" customWidth="1"/>
+    <col min="3" max="3" width="51.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="C11" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A16" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>10</v>
+      <c r="B16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
